--- a/data/trans_camb/IP2002-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP2002-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 4,14</t>
+          <t>-5,18; 3,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 5,35</t>
+          <t>-4,65; 4,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 3,89</t>
+          <t>-5,36; 3,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 6,4</t>
+          <t>-4,68; 6,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 0,51</t>
+          <t>-9,18; 0,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,05; -0,12</t>
+          <t>-9,06; -0,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 3,96</t>
+          <t>-3,34; 3,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 1,1</t>
+          <t>-5,51; 1,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 0,16</t>
+          <t>-6,41; 0,33</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-66,98; 124,87</t>
+          <t>-65,55; 115,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-61,33; 148,15</t>
+          <t>-62,32; 121,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,18; 124,91</t>
+          <t>-68,23; 92,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-45,24; 123,07</t>
+          <t>-44,51; 134,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,67; 14,89</t>
+          <t>-83,81; 18,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,52; 8,72</t>
+          <t>-82,79; 10,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,24; 77,98</t>
+          <t>-40,49; 78,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,14; 28,11</t>
+          <t>-63,45; 31,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-68,95; 9,14</t>
+          <t>-72,75; 9,78</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 4,35</t>
+          <t>-4,28; 4,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 2,89</t>
+          <t>-5,52; 2,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 4,57</t>
+          <t>-5,49; 3,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 2,57</t>
+          <t>-5,88; 2,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 1,27</t>
+          <t>-7,18; 1,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 0,1</t>
+          <t>-7,87; 0,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 2,49</t>
+          <t>-3,79; 1,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 0,88</t>
+          <t>-5,03; 0,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 0,5</t>
+          <t>-5,61; 0,57</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,69; 72,33</t>
+          <t>-42,02; 75,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-51,87; 51,85</t>
+          <t>-52,46; 43,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-50,36; 75,76</t>
+          <t>-52,56; 61,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,23; 42,15</t>
+          <t>-54,23; 36,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,3; 22,31</t>
+          <t>-63,84; 22,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,77; 8,03</t>
+          <t>-69,77; 16,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,63; 37,12</t>
+          <t>-38,31; 28,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,37; 13,95</t>
+          <t>-49,5; 12,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-54,79; 8,69</t>
+          <t>-54,61; 9,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 4,95</t>
+          <t>-4,09; 4,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 1,24</t>
+          <t>-6,48; 1,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 2,99</t>
+          <t>-5,43; 2,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 4,31</t>
+          <t>-6,02; 4,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,68; -0,45</t>
+          <t>-9,12; -0,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 4,52</t>
+          <t>-6,34; 4,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 3,35</t>
+          <t>-3,67; 3,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,59; -0,71</t>
+          <t>-6,75; -0,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 2,05</t>
+          <t>-4,74; 2,35</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,39; 127,56</t>
+          <t>-50,56; 129,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-77,56; 38,19</t>
+          <t>-76,04; 48,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-71,48; 80,31</t>
+          <t>-66,34; 80,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-55,13; 76,5</t>
+          <t>-54,36; 86,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-83,53; 2,99</t>
+          <t>-81,3; -1,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-60,17; 91,65</t>
+          <t>-59,68; 73,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,72; 67,82</t>
+          <t>-41,93; 65,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,71; -5,89</t>
+          <t>-71,87; 0,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-52,56; 42,89</t>
+          <t>-53,13; 44,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,45; -1,71</t>
+          <t>-8,96; -1,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 4,38</t>
+          <t>-4,43; 4,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 2,95</t>
+          <t>-5,82; 3,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 3,82</t>
+          <t>-3,47; 3,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 4,71</t>
+          <t>-2,9; 4,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 3,7</t>
+          <t>-4,04; 3,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 0,15</t>
+          <t>-5,3; -0,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 3,5</t>
+          <t>-2,57; 3,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 1,94</t>
+          <t>-4,01; 1,83</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-89,64; -25,77</t>
+          <t>-89,21; -15,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-47,11; 86,05</t>
+          <t>-45,62; 104,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,43; 61,77</t>
+          <t>-59,66; 67,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-58,66; 131,46</t>
+          <t>-56,02; 119,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,76; 166,62</t>
+          <t>-50,33; 143,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,23; 111,18</t>
+          <t>-65,77; 130,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-68,42; 0,69</t>
+          <t>-67,79; 1,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-33,37; 74,76</t>
+          <t>-34,21; 63,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-50,39; 42,29</t>
+          <t>-53,21; 37,71</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,76</t>
+          <t>-3,96; 0,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,29</t>
+          <t>-3,2; 1,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,11</t>
+          <t>-3,52; 1,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 1,86</t>
+          <t>-2,59; 1,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,54; -0,19</t>
+          <t>-4,44; -0,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,15</t>
+          <t>-4,5; -0,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,66</t>
+          <t>-2,46; 0,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,23; -0,23</t>
+          <t>-3,19; -0,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,35; -0,11</t>
+          <t>-3,38; -0,18</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-45,78; 13,39</t>
+          <t>-47,71; 7,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,31; 21,72</t>
+          <t>-36,57; 27,92</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-43,44; 17,79</t>
+          <t>-41,86; 19,28</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 32,18</t>
+          <t>-31,11; 29,8</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-54,09; -2,18</t>
+          <t>-52,49; -2,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-52,38; 3,16</t>
+          <t>-53,73; -2,18</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-31,82; 10,09</t>
+          <t>-30,91; 10,48</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-40,37; -3,14</t>
+          <t>-40,41; 0,01</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-41,14; -1,49</t>
+          <t>-41,82; -2,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2002-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP2002-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 3,85</t>
+          <t>-5,03; 3,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 4,91</t>
+          <t>-4,94; 4,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 3,09</t>
+          <t>-4,88; 3,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 6,77</t>
+          <t>-4,07; 7,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 0,4</t>
+          <t>-8,36; 0,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,06; -0,25</t>
+          <t>-8,64; 0,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 3,93</t>
+          <t>-3,36; 3,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 1,46</t>
+          <t>-5,27; 1,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 0,33</t>
+          <t>-6,27; 0,38</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-65,55; 115,81</t>
+          <t>-64,45; 121,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,32; 121,67</t>
+          <t>-64,6; 145,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-68,23; 92,14</t>
+          <t>-67,13; 125,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,51; 134,57</t>
+          <t>-41,15; 138,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-83,81; 18,82</t>
+          <t>-81,37; 34,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,79; 10,54</t>
+          <t>-83,26; 16,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,49; 78,24</t>
+          <t>-41,66; 78,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,45; 31,15</t>
+          <t>-64,22; 22,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-72,75; 9,78</t>
+          <t>-69,93; 11,24</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 4,54</t>
+          <t>-4,12; 4,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 2,65</t>
+          <t>-5,28; 3,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 3,84</t>
+          <t>-5,3; 4,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 2,55</t>
+          <t>-5,64; 2,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 1,24</t>
+          <t>-6,86; 1,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 0,59</t>
+          <t>-7,52; 0,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 1,99</t>
+          <t>-3,87; 2,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 0,77</t>
+          <t>-4,91; 0,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 0,57</t>
+          <t>-5,3; 0,56</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,02; 75,4</t>
+          <t>-40,3; 83,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-52,46; 43,43</t>
+          <t>-49,77; 67,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,56; 61,93</t>
+          <t>-52,51; 71,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-54,23; 36,72</t>
+          <t>-52,2; 45,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,84; 22,18</t>
+          <t>-65,61; 17,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,77; 16,73</t>
+          <t>-68,34; 9,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 28,5</t>
+          <t>-38,9; 34,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,5; 12,75</t>
+          <t>-49,73; 15,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-54,61; 9,46</t>
+          <t>-54,05; 12,9</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 4,92</t>
+          <t>-4,09; 5,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 1,63</t>
+          <t>-6,47; 1,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 2,99</t>
+          <t>-5,9; 2,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 4,45</t>
+          <t>-5,88; 4,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -0,51</t>
+          <t>-9,16; 0,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 4,04</t>
+          <t>-6,44; 5,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 3,62</t>
+          <t>-3,53; 3,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,75; -0,55</t>
+          <t>-6,74; -0,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 2,35</t>
+          <t>-4,55; 2,15</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-50,56; 129,71</t>
+          <t>-51,18; 155,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,04; 48,28</t>
+          <t>-75,12; 62,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-66,34; 80,38</t>
+          <t>-71,32; 71,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,36; 86,03</t>
+          <t>-54,59; 73,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-81,3; -1,92</t>
+          <t>-81,4; 11,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-59,68; 73,59</t>
+          <t>-56,98; 89,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,93; 65,96</t>
+          <t>-40,87; 58,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-71,87; 0,41</t>
+          <t>-73,58; -8,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-53,13; 44,87</t>
+          <t>-49,76; 40,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,96; -1,29</t>
+          <t>-9,48; -1,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 4,97</t>
+          <t>-4,69; 4,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 3,51</t>
+          <t>-5,46; 3,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 3,86</t>
+          <t>-3,77; 3,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 4,55</t>
+          <t>-2,95; 4,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 3,37</t>
+          <t>-4,35; 3,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,3; -0,12</t>
+          <t>-5,09; 0,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 3,32</t>
+          <t>-2,26; 3,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,83</t>
+          <t>-3,65; 1,92</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-89,21; -15,19</t>
+          <t>-88,7; -19,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,62; 104,04</t>
+          <t>-47,7; 88,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,66; 67,0</t>
+          <t>-56,28; 61,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,02; 119,55</t>
+          <t>-58,34; 135,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,33; 143,63</t>
+          <t>-47,96; 168,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,77; 130,06</t>
+          <t>-67,69; 119,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-67,79; 1,08</t>
+          <t>-66,6; 6,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,21; 63,8</t>
+          <t>-30,34; 74,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,21; 37,71</t>
+          <t>-50,58; 41,03</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 0,49</t>
+          <t>-3,85; 0,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 1,5</t>
+          <t>-3,12; 1,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 1,11</t>
+          <t>-3,55; 0,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,92</t>
+          <t>-2,55; 1,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,44; -0,26</t>
+          <t>-4,59; -0,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,5; -0,21</t>
+          <t>-4,43; -0,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,66</t>
+          <t>-2,59; 0,65</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,19; -0,0</t>
+          <t>-3,21; -0,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,38; -0,18</t>
+          <t>-3,4; -0,18</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-47,71; 7,83</t>
+          <t>-46,26; 9,04</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-36,57; 27,92</t>
+          <t>-38,22; 23,18</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,86; 19,28</t>
+          <t>-43,62; 16,33</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-31,11; 29,8</t>
+          <t>-30,37; 30,76</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-52,49; -2,5</t>
+          <t>-53,54; -5,19</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-53,73; -2,18</t>
+          <t>-53,64; 0,07</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-30,91; 10,48</t>
+          <t>-32,53; 9,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-40,41; 0,01</t>
+          <t>-39,69; -0,41</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-41,82; -2,1</t>
+          <t>-42,41; -2,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2002-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP2002-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,95</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-4,4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,73</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,24</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,95</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-4,37</t>
+          <t>-0,87</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,79</t>
+          <t>-2,7</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 3,91</t>
+          <t>-4,33; 6,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 4,95</t>
+          <t>-8,7; 0,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 3,92</t>
+          <t>-9,14; -0,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 7,31</t>
+          <t>-5,31; 4,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 0,94</t>
+          <t>-4,7; 5,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 0,39</t>
+          <t>-5,16; 4,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 3,97</t>
+          <t>-3,32; 3,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 1,04</t>
+          <t>-5,47; 1,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 0,38</t>
+          <t>-5,8; 0,4</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>14,66%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-50,6%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-56,41%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-12,68%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-4,23%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-17,36%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14,66%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-50,6%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-55,99%</t>
+          <t>-15,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-40,94%</t>
+          <t>-39,58%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-64,45; 121,61</t>
+          <t>-45,24; 123,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-64,6; 145,13</t>
+          <t>-82,67; 14,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,13; 125,09</t>
+          <t>-85,73; 4,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,15; 138,03</t>
+          <t>-66,98; 124,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,37; 34,8</t>
+          <t>-61,33; 148,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-83,26; 16,71</t>
+          <t>-65,79; 132,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,66; 78,55</t>
+          <t>-39,24; 77,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,22; 22,14</t>
+          <t>-64,14; 28,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,93; 11,24</t>
+          <t>-68,47; 10,43</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,61</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,92</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,65</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-1,07</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,61</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,92</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,69</t>
+          <t>-1,25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,41</t>
+          <t>-2,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 4,78</t>
+          <t>-5,62; 2,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 3,47</t>
+          <t>-7,24; 1,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 4,5</t>
+          <t>-7,99; 0,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 2,71</t>
+          <t>-4,84; 4,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 1,01</t>
+          <t>-5,78; 2,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 0,47</t>
+          <t>-5,65; 3,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 2,28</t>
+          <t>-3,73; 2,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 0,91</t>
+          <t>-5,17; 0,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 0,56</t>
+          <t>-5,58; 0,21</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-18,56%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-33,68%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-42,03%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-12,92%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-9,07%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-18,56%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-33,68%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-42,51%</t>
+          <t>-15,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-28,42%</t>
+          <t>-30,43%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,3; 83,72</t>
+          <t>-52,23; 42,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-49,77; 67,27</t>
+          <t>-65,3; 22,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,51; 71,33</t>
+          <t>-69,78; 7,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,2; 45,71</t>
+          <t>-44,69; 72,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,61; 17,06</t>
+          <t>-51,87; 51,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,34; 9,61</t>
+          <t>-54,84; 61,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,9; 34,23</t>
+          <t>-38,63; 37,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,73; 15,65</t>
+          <t>-50,37; 13,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-54,05; 12,9</t>
+          <t>-56,29; 4,47</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,7</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-4,79</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-1,08</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,38</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-2,22</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,27</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,79</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,07</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,22</t>
+          <t>-0,61</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 5,46</t>
+          <t>-5,87; 4,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 1,72</t>
+          <t>-9,68; -0,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 2,82</t>
+          <t>-6,45; 4,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 4,33</t>
+          <t>-4,16; 4,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 0,25</t>
+          <t>-6,68; 1,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 5,06</t>
+          <t>-4,86; 4,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 3,17</t>
+          <t>-3,66; 3,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,74; -0,72</t>
+          <t>-6,59; -0,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 2,15</t>
+          <t>-3,92; 2,87</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-8,48%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-57,72%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-13,04%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>6,24%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-36,6%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-20,95%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-8,48%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-57,72%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-12,9%</t>
+          <t>-1,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-16,91%</t>
+          <t>-8,44%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-51,18; 155,87</t>
+          <t>-55,13; 76,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-75,12; 62,36</t>
+          <t>-83,53; 2,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-71,32; 71,05</t>
+          <t>-60,99; 87,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,59; 73,01</t>
+          <t>-52,39; 127,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-81,4; 11,85</t>
+          <t>-77,56; 38,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,98; 89,37</t>
+          <t>-59,69; 132,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,87; 58,55</t>
+          <t>-39,72; 67,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-73,58; -8,06</t>
+          <t>-72,71; -5,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-49,76; 40,03</t>
+          <t>-46,47; 54,3</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,82</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,93</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-5,19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,08</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,82</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>-1,22</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,1</t>
+          <t>-1,08</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,48; -1,6</t>
+          <t>-3,9; 3,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 4,59</t>
+          <t>-2,89; 4,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 3,15</t>
+          <t>-4,25; 3,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 3,93</t>
+          <t>-9,45; -1,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 4,69</t>
+          <t>-4,43; 4,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 3,2</t>
+          <t>-5,7; 3,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 0,26</t>
+          <t>-5,14; 0,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 3,59</t>
+          <t>-2,69; 3,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 1,92</t>
+          <t>-3,92; 1,86</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>17,23%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-19,63%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-68,21%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-1,01%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-17,89%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-15,72%</t>
+          <t>-15,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-17,76%</t>
+          <t>-17,55%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-88,7; -19,89</t>
+          <t>-58,66; 131,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-47,7; 88,37</t>
+          <t>-46,76; 166,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-56,28; 61,72</t>
+          <t>-69,62; 111,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-58,34; 135,8</t>
+          <t>-89,64; -25,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,96; 168,0</t>
+          <t>-47,11; 86,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,69; 119,24</t>
+          <t>-59,24; 66,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-66,6; 6,58</t>
+          <t>-68,42; 0,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,34; 74,8</t>
+          <t>-33,37; 74,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-50,58; 41,03</t>
+          <t>-50,6; 43,22</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,35</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-2,47</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-2,31</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,57</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,89</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,18</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-2,47</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-0,94</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,75</t>
+          <t>-1,66</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 0,52</t>
+          <t>-2,62; 1,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,38</t>
+          <t>-4,54; -0,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,99</t>
+          <t>-4,32; 0,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,92</t>
+          <t>-3,76; 0,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,59; -0,35</t>
+          <t>-3,15; 1,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,43; -0,03</t>
+          <t>-3,29; 1,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,65</t>
+          <t>-2,57; 0,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,21; -0,07</t>
+          <t>-3,23; -0,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,4; -0,18</t>
+          <t>-3,25; -0,03</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-4,85%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-33,93%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-31,66%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-22,12%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-12,54%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-16,64%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-4,85%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-33,93%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-31,07%</t>
+          <t>-13,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-24,38%</t>
+          <t>-23,0%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-46,26; 9,04</t>
+          <t>-31,7; 32,18</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,22; 23,18</t>
+          <t>-54,09; -2,18</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 16,33</t>
+          <t>-52,1; 1,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 30,76</t>
+          <t>-45,78; 13,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-53,54; -5,19</t>
+          <t>-39,31; 21,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-53,64; 0,07</t>
+          <t>-39,33; 23,26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-32,53; 9,75</t>
+          <t>-31,82; 10,09</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-39,69; -0,41</t>
+          <t>-40,37; -3,14</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-42,41; -2,52</t>
+          <t>-40,37; 0,26</t>
         </is>
       </c>
     </row>
